--- a/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（组合场景）.xlsx
+++ b/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（组合场景）.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>name</t>
   </si>
@@ -56,18 +56,6 @@
   </si>
   <si>
     <t>1、查询成功，返回0条记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find({ &lt;字段名1&gt;: { &lt;匹配符&gt;: { $field: &lt;字段名2&gt; } }), ...}查询，覆盖测试：t1字段不存在、t2字段不存在
-2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{ &lt;字段名1&gt;: { $field: &lt;字段名2&gt; }, ...}
-查询，其他所有匹配符组合使用，如：
-find( { t1: { $gt: { $field: "t2" } } } )）
-2、检查查询结果正确性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -147,31 +135,31 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
@@ -233,31 +221,31 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I4" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
   <autoFilter ref="A1:I4"/>
   <tableColumns count="9">
-    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="0">
+    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="8">
+    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="7">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/summary" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="7">
+    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/preconditions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="6">
+    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="5">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/execution_type" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="5">
+    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="4">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/importance" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="4">
+    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="3">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/step_number" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="3">
+    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="2">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/actions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="2">
+    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="1">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/expectedresults" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="1">
+    <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="0">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/execution_type" xmlDataType="integer"/>
     </tableColumn>
   </tableColumns>
@@ -592,9 +580,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="54">
+    <row r="2" spans="1:9" ht="27">
       <c r="A2" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -608,19 +596,17 @@
       <c r="F2" s="3">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="G2" s="2"/>
       <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="54">
-      <c r="A3" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -634,9 +620,7 @@
       <c r="F3" s="3">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
@@ -646,7 +630,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
